--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484279_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484279_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.443</v>
+        <v>6.0687</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4568</v>
+        <v>5.8995</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9863</v>
+        <v>0.1692</v>
       </c>
       <c r="G2" t="n">
         <v>2.8342</v>
@@ -610,13 +610,13 @@
         <v>1.1721</v>
       </c>
       <c r="S2" t="n">
-        <v>5.4888</v>
+        <v>3.1144</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0762</v>
+        <v>1.5189</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4126</v>
+        <v>1.5955</v>
       </c>
       <c r="V2" t="n">
         <v>1.0968</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8648</v>
+        <v>4.0482</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8037</v>
+        <v>3.8237</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0611</v>
+        <v>0.2245</v>
       </c>
       <c r="G3" t="n">
         <v>2.7802</v>
@@ -688,13 +688,13 @@
         <v>1.1721</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9413</v>
+        <v>2.1247</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9933999999999999</v>
+        <v>1.0133</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9479</v>
+        <v>1.1113</v>
       </c>
       <c r="V3" t="n">
         <v>1.0968</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6999</v>
+        <v>1.41</v>
       </c>
       <c r="E4" t="n">
-        <v>1.311</v>
+        <v>1.776</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6111</v>
+        <v>-0.366</v>
       </c>
       <c r="G4" t="n">
         <v>0.4686</v>
@@ -766,13 +766,13 @@
         <v>0.7814</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4831</v>
+        <v>0.227</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0689</v>
+        <v>0.5339</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.552</v>
+        <v>-0.3069</v>
       </c>
       <c r="V4" t="n">
         <v>-0.067</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2485</v>
+        <v>0.0297</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0156</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7671</v>
+        <v>-0.9658</v>
       </c>
       <c r="G5" t="n">
-        <v>3.022</v>
+        <v>-0.0446</v>
       </c>
       <c r="H5" t="n">
-        <v>3.319</v>
+        <v>1.547</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2971</v>
+        <v>-1.5916</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9626</v>
+        <v>2.0179</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9893</v>
+        <v>2.6644</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0266</v>
+        <v>-0.6465</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0593</v>
+        <v>-2.0625</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3298</v>
+        <v>-1.1174</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2704</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1488</v>
+        <v>-4.1022</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8358</v>
+        <v>1.2435</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9245</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0887</v>
+        <v>0.6009</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.4373</v>
+        <v>1.7609</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2772</v>
+        <v>2.4373</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.7145</v>
+        <v>-0.6763</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1514</v>
+        <v>-0.1149</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7328</v>
+        <v>1.5706</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8841</v>
+        <v>-1.6854</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0446</v>
+        <v>3.022</v>
       </c>
       <c r="H6" t="n">
-        <v>1.547</v>
+        <v>3.319</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5916</v>
+        <v>-0.2971</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0179</v>
+        <v>2.9626</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6644</v>
+        <v>2.9893</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6465</v>
+        <v>-0.0266</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0625</v>
+        <v>0.0593</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1174</v>
+        <v>0.3298</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-0.2704</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.9301</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.1022</v>
+        <v>-2.1488</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0625</v>
+        <v>0.4725</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3798</v>
+        <v>0.4795</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6827</v>
+        <v>-0.007</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7609</v>
+        <v>-2.4373</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4373</v>
+        <v>0.2772</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6763</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CARRERA PRAT</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7197</v>
+        <v>-1.5856</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3723</v>
+        <v>-2.4031</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3474</v>
+        <v>0.8176</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.3194</v>
+        <v>-1.9931</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0113</v>
+        <v>0.2443</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3081</v>
+        <v>-2.2375</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2259</v>
+        <v>-1.5689</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0819</v>
+        <v>1.2075</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3077</v>
+        <v>-2.7763</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0935</v>
+        <v>-0.4243</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0931</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0004</v>
+        <v>0.5389</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1271</v>
+        <v>0.1341</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4237</v>
+        <v>0.1424</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5508</v>
+        <v>-0.0083</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2772</v>
+        <v>0.6642</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>J. CARRERA PRAT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2122</v>
+        <v>-1.6398</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0298</v>
+        <v>-1.2107</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8176</v>
+        <v>-0.4291</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9931</v>
+        <v>-2.3194</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2443</v>
+        <v>-1.0113</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.2375</v>
+        <v>-1.3081</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5689</v>
+        <v>-1.2259</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2075</v>
+        <v>0.0819</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.7763</v>
+        <v>-1.3077</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4243</v>
+        <v>-1.0935</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-1.0931</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5389</v>
+        <v>-0.0004</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4925</v>
+        <v>0.207</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4842</v>
+        <v>-0.262</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0083</v>
+        <v>0.4691</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9242</v>
+        <v>-2.2958</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8744</v>
+        <v>1.3394</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.7986</v>
+        <v>-3.6352</v>
       </c>
       <c r="G9" t="n">
         <v>0.2555</v>
@@ -1156,13 +1156,13 @@
         <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5238</v>
+        <v>0.1046</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4237</v>
+        <v>0.0413</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1002</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>-3.0466</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9396</v>
+        <v>-4.0061</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8274</v>
+        <v>-2.2207</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1122</v>
+        <v>-1.7854</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8869</v>
@@ -1234,13 +1234,13 @@
         <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9542</v>
+        <v>-0.0207</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.1196</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2279</v>
+        <v>0.0989</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3405</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.309099999999999</v>
+        <v>1.9144</v>
       </c>
       <c r="E11" t="n">
-        <v>8.9648</v>
+        <v>9.5702</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.6555</v>
+        <v>-7.655600000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>4.116500000000001</v>
+        <v>4.1165</v>
       </c>
       <c r="H11" t="n">
         <v>7.4879</v>
@@ -1303,28 +1303,28 @@
         <v>-1.355</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.8137</v>
+        <v>-7.813699999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>-15.6274</v>
       </c>
       <c r="R11" t="n">
-        <v>7.813799999999999</v>
+        <v>7.813800000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>7.0019</v>
+        <v>7.6071</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3849</v>
+        <v>3.9903</v>
       </c>
       <c r="U11" t="n">
-        <v>3.6169</v>
+        <v>3.6167</v>
       </c>
       <c r="V11" t="n">
         <v>-1.9955</v>
       </c>
       <c r="W11" t="n">
-        <v>5.7061</v>
+        <v>5.706099999999999</v>
       </c>
       <c r="X11" t="n">
         <v>-7.7017</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.917</v>
+        <v>2.4033</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3534</v>
+        <v>1.6567</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5636</v>
+        <v>0.7466</v>
       </c>
       <c r="G12" t="n">
         <v>0.008999999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>2.7348</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1732</v>
+        <v>-0.3405</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6574</v>
+        <v>-0.3541</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8306</v>
+        <v>0.0136</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3387</v>
+        <v>0.9401</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7385</v>
+        <v>2.612</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6002</v>
+        <v>-1.6719</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.8571</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7705</v>
+        <v>-2.7844</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5371</v>
+        <v>3.6415</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8512</v>
+        <v>2.5146</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1228</v>
+        <v>-0.5884</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7284</v>
+        <v>3.103</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.08459999999999999</v>
+        <v>-1.6575</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8933</v>
+        <v>-2.196</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8087</v>
+        <v>0.5385</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1953</v>
+        <v>2.1488</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3768</v>
+        <v>-0.7923</v>
       </c>
       <c r="T13" t="n">
-        <v>0.864</v>
+        <v>-0.125</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5128</v>
+        <v>-0.6673</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6093</v>
+        <v>-1.2735</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.2224</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6093</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9517</v>
+        <v>0.7048</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8142</v>
+        <v>0.1318</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8625</v>
+        <v>0.573</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8571</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.7844</v>
+        <v>-0.7705</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6415</v>
+        <v>1.5371</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5146</v>
+        <v>0.8512</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5884</v>
+        <v>0.1228</v>
       </c>
       <c r="L14" t="n">
-        <v>3.103</v>
+        <v>0.7284</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6575</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.196</v>
+        <v>-0.8933</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5385</v>
+        <v>0.8087</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1488</v>
+        <v>0.7814</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7806999999999999</v>
+        <v>0.7429</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0772</v>
+        <v>0.2573</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.858</v>
+        <v>0.4855</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2735</v>
+        <v>-0.6093</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4959</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1537</v>
+        <v>0.282</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1311</v>
+        <v>2.2322</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9774</v>
+        <v>-1.9502</v>
       </c>
       <c r="G15" t="n">
         <v>0.0007</v>
@@ -1624,13 +1624,13 @@
         <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8237</v>
+        <v>-0.6954</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6657</v>
+        <v>-0.5646</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.158</v>
+        <v>-0.1308</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4005</v>
+        <v>-0.1052</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9725</v>
+        <v>0.8743</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3729</v>
+        <v>-0.9795</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.0591</v>
+        <v>-0.4253</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1412</v>
+        <v>0.6669</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9179</v>
+        <v>-1.0922</v>
       </c>
       <c r="J17" t="n">
-        <v>0.882</v>
+        <v>1.916</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3942</v>
+        <v>3.2771</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5122</v>
+        <v>-1.361</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.9411</v>
+        <v>-2.3413</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.5354</v>
+        <v>-2.6101</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4056</v>
+        <v>0.2688</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9534</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9534</v>
+        <v>2.3441</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5172</v>
+        <v>-2.0504</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2588</v>
+        <v>-1.068</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7759</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2224</v>
+        <v>3.9331</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8317</v>
+        <v>3.9331</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7742</v>
+        <v>-0.5326</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3687</v>
+        <v>1.568</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1429</v>
+        <v>-2.1006</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4253</v>
+        <v>-2.0591</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6669</v>
+        <v>-1.1412</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0922</v>
+        <v>-0.9179</v>
       </c>
       <c r="J18" t="n">
-        <v>1.916</v>
+        <v>0.882</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2771</v>
+        <v>1.3942</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.361</v>
+        <v>-0.5122</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3413</v>
+        <v>-2.9411</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.6101</v>
+        <v>-2.5354</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2688</v>
+        <v>-0.4056</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3441</v>
+        <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.7194</v>
+        <v>-0.6493</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.5736</v>
+        <v>-0.1457</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1458</v>
+        <v>-0.5036</v>
       </c>
       <c r="V18" t="n">
-        <v>3.9331</v>
+        <v>0.2224</v>
       </c>
       <c r="W18" t="n">
-        <v>3.9331</v>
+        <v>0.8317</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8559</v>
+        <v>-0.7432</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4711</v>
+        <v>0.7744</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.327</v>
+        <v>-1.5176</v>
       </c>
       <c r="G19" t="n">
         <v>0.3963</v>
@@ -1936,13 +1936,13 @@
         <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2057</v>
+        <v>-1.093</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9684</v>
+        <v>-0.665</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2373</v>
+        <v>-0.4279</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2186</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3212</v>
+        <v>-1.5433</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8201</v>
+        <v>-1.3145</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5011</v>
+        <v>-0.2288</v>
       </c>
       <c r="G20" t="n">
         <v>-0.96</v>
@@ -2014,13 +2014,13 @@
         <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.084</v>
+        <v>-0.3061</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.2812</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2972</v>
+        <v>-0.0248</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2772</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4532</v>
+        <v>-2.8498</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3736</v>
+        <v>-0.8792</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0796</v>
+        <v>-1.9706</v>
       </c>
       <c r="G21" t="n">
         <v>-2.8366</v>
@@ -2092,13 +2092,13 @@
         <v>2.5395</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4212</v>
+        <v>-1.8179</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1649</v>
+        <v>-0.6704</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2564</v>
+        <v>-1.1474</v>
       </c>
       <c r="V21" t="n">
         <v>1.2186</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3091</v>
+        <v>-1.309099999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>7.655799999999999</v>
+        <v>7.655699999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-8.9648</v>
+        <v>-8.964799999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.1165</v>
+        <v>-4.116499999999999</v>
       </c>
       <c r="H22" t="n">
         <v>-7.4879</v>
@@ -2161,7 +2161,7 @@
         <v>2.0164</v>
       </c>
       <c r="P22" t="n">
-        <v>7.813800000000001</v>
+        <v>7.813799999999999</v>
       </c>
       <c r="Q22" t="n">
         <v>-7.8137</v>
@@ -2170,13 +2170,13 @@
         <v>15.6275</v>
       </c>
       <c r="S22" t="n">
-        <v>-7.0019</v>
+        <v>-7.002</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.6168</v>
+        <v>-3.6167</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.3852</v>
+        <v>-3.3851</v>
       </c>
       <c r="V22" t="n">
         <v>1.9955</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484279_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484279_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1219</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1219</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.067</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.6763</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.7145</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-3.0466</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.6177</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,7 @@
       <c r="X11" t="n">
         <v>-7.7017</v>
       </c>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,11 +1458,16 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1479,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9401</v>
+        <v>0.7048</v>
       </c>
       <c r="E13" t="n">
-        <v>2.612</v>
+        <v>0.1318</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6719</v>
+        <v>0.573</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8571</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.7844</v>
+        <v>-0.7705</v>
       </c>
       <c r="I13" t="n">
-        <v>3.6415</v>
+        <v>1.5371</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5146</v>
+        <v>0.8512</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5884</v>
+        <v>0.1228</v>
       </c>
       <c r="L13" t="n">
-        <v>3.103</v>
+        <v>0.7284</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6575</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.196</v>
+        <v>-0.8933</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5385</v>
+        <v>0.8087</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1488</v>
+        <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7923</v>
+        <v>0.7429</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.125</v>
+        <v>0.2573</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6673</v>
+        <v>0.4855</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2735</v>
+        <v>-0.6093</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4959</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7048</v>
+        <v>0.607</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1318</v>
+        <v>0.607</v>
       </c>
       <c r="F14" t="n">
-        <v>0.573</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.607</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7705</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5371</v>
+        <v>0.607</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8512</v>
+        <v>0.607</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1228</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7284</v>
+        <v>0.607</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.08459999999999999</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8933</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8087</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7429</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2573</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4855</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.282</v>
+        <v>0.3331</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2322</v>
+        <v>2.005</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9502</v>
+        <v>-1.6719</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0007</v>
+        <v>0.2501</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2829</v>
+        <v>-2.7844</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2837</v>
+        <v>3.0345</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5782</v>
+        <v>1.9076</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0246</v>
+        <v>-0.5884</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5537</v>
+        <v>2.496</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5775</v>
+        <v>-1.6575</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3075</v>
+        <v>-2.196</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.27</v>
+        <v>0.5385</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6954</v>
+        <v>-0.7923</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5646</v>
+        <v>-0.125</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1308</v>
+        <v>-0.6673</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.2735</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2186</v>
+        <v>0.2224</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. TORRALBA CAROZ</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1348</v>
+        <v>0.282</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>2.2322</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1348</v>
+        <v>-1.9502</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1348</v>
+        <v>0.0007</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-0.2829</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1348</v>
+        <v>0.2837</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1.5782</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1.0246</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.5537</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1348</v>
+        <v>-1.5775</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-1.3075</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1348</v>
+        <v>-0.27</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.6954</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.5646</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.1308</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>D. TORRALBA CAROZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1052</v>
+        <v>0.1348</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8743</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9795</v>
+        <v>0.1348</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4253</v>
+        <v>0.1348</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6669</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0922</v>
+        <v>0.1348</v>
       </c>
       <c r="J17" t="n">
-        <v>1.916</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2771</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3413</v>
+        <v>0.1348</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.6101</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2688</v>
+        <v>0.1348</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.0504</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.068</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9824000000000001</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>3.9331</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.9331</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5326</v>
+        <v>-0.1052</v>
       </c>
       <c r="E18" t="n">
-        <v>1.568</v>
+        <v>0.8743</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1006</v>
+        <v>-0.9795</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.0591</v>
+        <v>-0.4253</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1412</v>
+        <v>0.6669</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9179</v>
+        <v>-1.0922</v>
       </c>
       <c r="J18" t="n">
-        <v>0.882</v>
+        <v>1.916</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3942</v>
+        <v>3.2771</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5122</v>
+        <v>-1.361</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.9411</v>
+        <v>-2.3413</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.5354</v>
+        <v>-2.6101</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4056</v>
+        <v>0.2688</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9534</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9534</v>
+        <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6493</v>
+        <v>-2.0504</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1457</v>
+        <v>-1.068</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5036</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2224</v>
+        <v>3.9331</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8317</v>
+        <v>3.9331</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7432</v>
+        <v>-0.5326</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7744</v>
+        <v>1.568</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5176</v>
+        <v>-2.1006</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3963</v>
+        <v>-2.0591</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7634</v>
+        <v>-1.1412</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1597</v>
+        <v>-0.9179</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4394</v>
+        <v>0.882</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8186</v>
+        <v>1.3942</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6208</v>
+        <v>-0.5122</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0431</v>
+        <v>-2.9411</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.582</v>
+        <v>-2.5354</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5389</v>
+        <v>-0.4056</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.093</v>
+        <v>-0.6493</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.665</v>
+        <v>-0.1457</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4279</v>
+        <v>-0.5036</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2186</v>
+        <v>0.2224</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.8317</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5433</v>
+        <v>-0.7432</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3145</v>
+        <v>0.7744</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2288</v>
+        <v>-1.5176</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.96</v>
+        <v>0.3963</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2865</v>
+        <v>-0.7634</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6735</v>
+        <v>1.1597</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0566</v>
+        <v>1.4394</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2906</v>
+        <v>0.8186</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3472</v>
+        <v>0.6208</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9034</v>
+        <v>-1.0431</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5771</v>
+        <v>-1.582</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6737</v>
+        <v>0.5389</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3061</v>
+        <v>-1.093</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2812</v>
+        <v>-0.665</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0248</v>
+        <v>-0.4279</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8498</v>
+        <v>-1.5433</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8792</v>
+        <v>-1.3145</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9706</v>
+        <v>-0.2288</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.8366</v>
+        <v>-0.96</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.7278</v>
+        <v>-0.2865</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1088</v>
+        <v>-0.6735</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2488</v>
+        <v>-0.0566</v>
       </c>
       <c r="K21" t="n">
-        <v>0.08690000000000001</v>
+        <v>1.2906</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1619</v>
+        <v>-1.3472</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.0854</v>
+        <v>-0.9034</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.8148</v>
+        <v>-1.5771</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2706</v>
+        <v>0.6737</v>
       </c>
       <c r="P21" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5395</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.8179</v>
+        <v>-0.3061</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6704</v>
+        <v>-0.2812</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1474</v>
+        <v>-0.0248</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,68 +2226,152 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
+        <v>-2.8498</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.8792</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-1.9706</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-2.8366</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-2.7278</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.1088</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.2488</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.08690000000000001</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-3.0854</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-2.8148</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.2706</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.5395</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-1.8179</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.6704</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-1.1474</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484279_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
         <v>-1.309099999999999</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>7.655699999999999</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>-8.964799999999999</v>
       </c>
-      <c r="G22" t="n">
-        <v>-4.116499999999999</v>
-      </c>
-      <c r="H22" t="n">
+      <c r="G23" t="n">
+        <v>-4.1165</v>
+      </c>
+      <c r="H23" t="n">
         <v>-7.4879</v>
       </c>
-      <c r="I22" t="n">
-        <v>3.3714</v>
-      </c>
-      <c r="J22" t="n">
+      <c r="I23" t="n">
+        <v>3.371399999999999</v>
+      </c>
+      <c r="J23" t="n">
         <v>11.3844</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>10.0294</v>
       </c>
-      <c r="L22" t="n">
-        <v>1.355200000000001</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="L23" t="n">
+        <v>1.3552</v>
+      </c>
+      <c r="M23" t="n">
         <v>-15.5009</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>-17.5172</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>2.0164</v>
       </c>
-      <c r="P22" t="n">
-        <v>7.813799999999999</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="P23" t="n">
+        <v>7.813800000000001</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-7.8137</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>15.6275</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
         <v>-7.002</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>-3.6167</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>-3.3851</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V23" t="n">
         <v>1.9955</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W23" t="n">
         <v>7.7017</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X23" t="n">
         <v>-5.706099999999999</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
